--- a/daily_matches/job_matches_2026-03-24.xlsx
+++ b/daily_matches/job_matches_2026-03-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Research Biology</t>
+          <t>Machine Learning Engineer - AI team</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.3</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, NoSQL, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, Azure ML, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,137 +496,137 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15a9b9f7b9af1bd1</t>
+          <t>https://www.indeed.com/viewjob?jk=6a74ced656aae12e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Infrastructure Engineer</t>
+          <t>Senior Data Engineer - Remote USA (*eligible states)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Glyphic Biotechnologies</t>
+          <t>The RealReal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, BigQuery, Data Lake, Docker, Snowflake, BigQuery, PostgreSQL, Python, SQL</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Redshift, BigQuery, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e4470d7d64962ba</t>
+          <t>https://www.indeed.com/viewjob?jk=9240be517a54d28f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>App Dev &amp; Support Engineer II</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Elixir Technologies</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ojai, CA, US USA</t>
+          <t>Somerset, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Python, R, Java</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a724ee3a9b6bd5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=1ef4e0f09fbc2537</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III (Contract Talent)</t>
+          <t>Developer IV</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Robert Half</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, Data Lake, Docker, Kubernetes, CI/CD, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=136af0e8060c5b22</t>
+          <t>https://www.indeed.com/viewjob?jk=faa1324dfb34b3df</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Frontend Developer, 3D - Web</t>
+          <t>Software Engineer II (AI, Python, Typescript)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zillow</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, Git, Kafka, R, Java, Scala, Optimization</t>
+          <t>RAG, AKS, CI/CD, Jenkins, Terraform, Git, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c080737276191b3</t>
+          <t>https://www.indeed.com/viewjob?jk=a84f414aae298ba7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer - CloudOps</t>
+          <t>App Dev &amp; Support Engineer III</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gallagher Group</t>
+          <t>Conduent</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Somerset, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, CI/CD, Jenkins, GitHub Actions, Git, Python, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,42 +671,182 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd5d7a01ae2fbcfb</t>
+          <t>https://www.indeed.com/viewjob?jk=ce35802658abfa34</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer - Snowflake</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Jenkins, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f7e36064fcccf83f</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AI Architect</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Trader Interactive</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Virginia Beach, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, R</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0b36de9f9a42122</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Java Developer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Conduent</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Kafka, MongoDB, R, Java</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f423abaf086a5787</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Engineer (AI Driven Software Engineering, Java, Spring Boot, AWS) Remote</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Mutual of Omaha</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, MongoDB, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e21f35e2c18b14a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>10</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, Git, Snowflake, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>2026-03-23</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d1584ac2c7284f13</t>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=894d23b3bea2fdc3</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-24.xlsx
+++ b/daily_matches/job_matches_2026-03-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,130 +468,130 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer - AI team</t>
+          <t>CD Excellence Data Engineering Associate</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Unilever</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Englewood Cliffs, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, XGBoost, Azure ML, Docker, Kubernetes</t>
+          <t>Data Scientist, RAG, Prompt Engineering, Azure ML, Synapse, Data Lake, CI/CD, GitHub Actions, Git, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a74ced656aae12e</t>
+          <t>https://www.indeed.com/viewjob?jk=c49b3555427c9f7a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote USA (*eligible states)</t>
+          <t>AI Engineer – Agentic Systems (4–7 Years Experience)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The RealReal</t>
+          <t>Vikara.AI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Redshift, BigQuery, Docker, Kubernetes, Git</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9240be517a54d28f</t>
+          <t>https://www.indeed.com/viewjob?jk=35a669990dfd99e8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>App Dev &amp; Support Engineer II</t>
+          <t>Full Stack Developer Intern</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Somerset, NJ, US USA</t>
+          <t>Westford, MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Machine Learning Engineer, RAG, PyTorch, Docker, Kubernetes, CI/CD, Terraform, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ef4e0f09fbc2537</t>
+          <t>https://www.indeed.com/viewjob?jk=e6d07eb218f7af80</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Developer IV</t>
+          <t>Associate</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>LatentView Analytics</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, Data Lake, Docker, Kubernetes, CI/CD, Kafka</t>
+          <t>RAG, Redshift, BigQuery, Git, BigQuery, Redshift, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faa1324dfb34b3df</t>
+          <t>https://www.indeed.com/viewjob?jk=07938dfe3d697c4c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer II (AI, Python, Typescript)</t>
+          <t>Senior Software Engineer, Research Biology</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, AKS, CI/CD, Jenkins, Terraform, Git, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>RAG, Data Lake, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,59 +636,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a84f414aae298ba7</t>
+          <t>https://www.indeed.com/viewjob?jk=b7788ee0fe043ede</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>App Dev &amp; Support Engineer III</t>
+          <t>Senior Data Engineer (Python &amp; Snowflake)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>3Pillar Global</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Somerset, NJ, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, CI/CD, Jenkins, GitHub Actions, Git, Python, R</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Snowflake, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce35802658abfa34</t>
+          <t>https://www.indeed.com/viewjob?jk=bff80065b4fd4799</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>New College Grad - Software Development Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, Terraform, Git, Python, R, Java, Scala</t>
+          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, Git, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7e36064fcccf83f</t>
+          <t>https://www.indeed.com/viewjob?jk=e8c7960ffe6780df</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Trader Interactive</t>
+          <t>Marmon Foodservice Technologies</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Carol Stream, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,69 +731,69 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, R</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Data Lake, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0b36de9f9a42122</t>
+          <t>https://www.indeed.com/viewjob?jk=67e70f37a93946c0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>QA Automation Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Conduent</t>
+          <t>Upland Software</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Kafka, MongoDB, R, Java</t>
+          <t>RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f423abaf086a5787</t>
+          <t>https://www.indeed.com/viewjob?jk=42d157dadee8d8e7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Engineer (AI Driven Software Engineering, Java, Spring Boot, AWS) Remote</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,52 +801,297 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, MongoDB, R, Java, Scala</t>
+          <t>RAG, Copilot, Docker, Kubernetes, Git, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e21f35e2c18b14a8</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b27b51ab8b425f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Full Stack Software Development Engineer</t>
+          <t>Associate Research Scientist (Weiss Lab)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>New York University</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, Keras, CI/CD, Git, Matplotlib, Seaborn, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b13f4c4d39f78aa7</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Software Engineer 1 - FS</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Intuit</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>10</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>CI/CD, PostgreSQL, MySQL, MongoDB, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=499aea438510dd89</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Vikara.AI</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AI Engineer, Git, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26530706c4353018</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PingOne Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=03d0498fa84b3568</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Westford, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, CI/CD, PostgreSQL, MySQL, MongoDB, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72d32d201a7ea121</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Micron Technology</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, Git, NoSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>2026-03-23</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=894d23b3bea2fdc3</t>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de3e51d72c8015c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Software Engineer — Public Safety Cloud Integrations</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Tyler Technologies</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Troy, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>S3, Docker, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ca08f99f806234c</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>OpenAM</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ee4d114011297e1</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-24.xlsx
+++ b/daily_matches/job_matches_2026-03-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CD Excellence Data Engineering Associate</t>
+          <t>AI/Machine Learning Engineer - Python | TheLoops</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Unilever</t>
+          <t>IFS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Englewood Cliffs, NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Azure ML, Synapse, Data Lake, CI/CD, GitHub Actions, Git, Databricks</t>
+          <t>Machine Learning Engineer, LangChain, RAG, Hugging Face, Pinecone, Prompt Engineering, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c49b3555427c9f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=b47b666d9d70dada</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Engineer – Agentic Systems (4–7 Years Experience)</t>
+          <t>Digital Customer Engagement AI Data Scientist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vikara.AI</t>
+          <t>Siemens Healthineers</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Git, Snowflake, Databricks, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35a669990dfd99e8</t>
+          <t>https://www.indeed.com/viewjob?jk=f4ef1d377bcc5497</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Full Stack Developer Intern</t>
+          <t>AI Engineer - Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fortegra</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Westford, MA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, PyTorch, Docker, Kubernetes, CI/CD, Terraform, NoSQL, Python, SQL</t>
+          <t>AI Engineer, Copilot, Prompt Engineering, FastAPI, CI/CD, Git, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6d07eb218f7af80</t>
+          <t>https://www.indeed.com/viewjob?jk=5e03f16f1cbf826a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>Technology Engineer Senior</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LatentView Analytics</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Git, BigQuery, Redshift, Tableau, Python, SQL, R</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07938dfe3d697c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=2bdcc46265260933</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Research Biology</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Press Ganey</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, NoSQL, Python, SQL</t>
+          <t>Data Scientist, RAG, Hadoop, Tableau, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7788ee0fe043ede</t>
+          <t>https://www.indeed.com/viewjob?jk=4708b1b61958a5f8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python &amp; Snowflake)</t>
+          <t>Senior AI Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3Pillar Global</t>
+          <t>Arctic Wolf Networks</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Snowflake, Python, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, CI/CD, Databricks, Kafka, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,427 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bff80065b4fd4799</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>New College Grad - Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Micron Technology</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, Git, NoSQL, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e8c7960ffe6780df</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Marmon Foodservice Technologies</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Carol Stream, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Data Lake, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=67e70f37a93946c0</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>QA Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Upland Software</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=42d157dadee8d8e7</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Micron Technology</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, Kubernetes, Git, NoSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b27b51ab8b425f</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Associate Research Scientist (Weiss Lab)</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>New York University</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>TensorFlow, PyTorch, Keras, CI/CD, Git, Matplotlib, Seaborn, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b13f4c4d39f78aa7</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Software Engineer 1 - FS</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Intuit</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Mountain View, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CI/CD, PostgreSQL, MySQL, MongoDB, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=499aea438510dd89</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Vikara.AI</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>AI Engineer, Git, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=26530706c4353018</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>PingOne Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RAG, S3, EC2, Kubernetes, CI/CD, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=03d0498fa84b3568</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Westford, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, CI/CD, PostgreSQL, MySQL, MongoDB, NoSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=72d32d201a7ea121</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Micron Technology</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, Kubernetes, Git, NoSQL, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=de3e51d72c8015c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Software Engineer — Public Safety Cloud Integrations</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Tyler Technologies</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Troy, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>S3, Docker, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2ca08f99f806234c</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>OpenAM</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7ee4d114011297e1</t>
+          <t>https://www.indeed.com/viewjob?jk=06b896137ad25852</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-24.xlsx
+++ b/daily_matches/job_matches_2026-03-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Engineer - Python | TheLoops</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IFS</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Hugging Face, Pinecone, Prompt Engineering, CI/CD, Git, Python, R</t>
+          <t>Generative AI, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b47b666d9d70dada</t>
+          <t>https://www.indeed.com/viewjob?jk=1cec5fe386ea9e81</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Digital Customer Engagement AI Data Scientist</t>
+          <t>Salesforce AI / Einstein Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Siemens Healthineers</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Git, Snowflake, Databricks, Python</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ef1d377bcc5497</t>
+          <t>https://www.indeed.com/viewjob?jk=2e26b8f2a42544e0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer - Data Engineer</t>
+          <t>Senior AI Security Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fortegra</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Copilot, Prompt Engineering, FastAPI, CI/CD, Git, R, Scala, Optimization</t>
+          <t>RAG, Pinecone, S3, EC2, Glue, Athena, Kinesis, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e03f16f1cbf826a</t>
+          <t>https://www.indeed.com/viewjob?jk=d83c4d4db97873d5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Technology Engineer Senior</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, R, Java, Scala, Optimization</t>
+          <t>RAG, Copilot, Synapse, FastAPI, Docker, CI/CD, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bdcc46265260933</t>
+          <t>https://www.indeed.com/viewjob?jk=1307a713db0f777e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Hadoop, Tableau, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, LangChain, FAISS, Pinecone, TensorFlow, PyTorch, Docker, CI/CD, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,42 +636,637 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4708b1b61958a5f8</t>
+          <t>https://www.indeed.com/viewjob?jk=2e13a41dc86b5f36</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior AI Developer</t>
+          <t>Salesforce AI / Einstein Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Arctic Wolf Networks</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Databricks, PySpark, Python</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1dc72753ea7cc45</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AI/Machine Learning Engineer - Python | TheLoops</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>IFS</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, LangChain, RAG, Hugging Face, Pinecone, Prompt Engineering, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7dbda87738776d31</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Lebanon, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=194261bb31192fd7</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d9a4c8885c90b5e</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Salesforce AI / Einstein Developer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Databricks, PySpark, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1de12f8e3dbaff6a</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PingOne Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Python, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=77901b3684582750</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AI Data Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Plante Moran</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Southfield, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, Databricks, PySpark, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39cd370d20d11526</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Specialist - Data Sciences</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LTIMindtree</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, TensorFlow, PyTorch, FastAPI, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27e9c6f1ee3f0d44</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CliftonLarsonAllen</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, CI/CD, Git, Databricks, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=70951b37d700924a</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>OpenAM</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8634ea4c64bebbd</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>App Dev &amp; Database Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Metropolitan Transportation Authority</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, MongoDB, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d90360aa81ba0097</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AI Developer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Global Linking Solutions</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f332ae252b459a91</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Integration Developer - Higher Education Exp Required</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Unitek Learning</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Kafka, PostgreSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d8c7c0b2b396d994</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Servpro Industries</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Gallatin, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Git, Tableau, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3821e24a55046e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Consultant, Full Stack Engineer - Digital &amp; Insights</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>FTI Consulting, Inc.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=539b056b17636737</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Software Engineer - FS/FE</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Rent the Runway</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Brooklyn, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, MySQL, MongoDB, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31fdbe21f7b1ae69</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CrowdStrike AI Security Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Generative AI, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8396490895a99087</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Mid-Senior Python/TensorFlow Developer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Devengine</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D24" t="n">
         <v>10</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, CI/CD, Databricks, Kafka, R, Scala</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=06b896137ad25852</t>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, Copilot, TensorFlow, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=385506505ec07794</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-24.xlsx
+++ b/daily_matches/job_matches_2026-03-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>Data Scientist I &amp; II</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FedEx</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>26.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, BigQuery, Synapse, Dataflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cec5fe386ea9e81</t>
+          <t>https://www.indeed.com/viewjob?jk=cc7cdb95523374c3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Salesforce AI / Einstein Developer</t>
+          <t>Senior AI Engineer, MarTech</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>25.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Snowflake, Databricks</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, TensorFlow, PyTorch, AWS SageMaker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e26b8f2a42544e0</t>
+          <t>https://www.indeed.com/viewjob?jk=1daebb30fd5fc85c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior AI Security Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tror</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Pinecone, S3, EC2, Glue, Athena, Kinesis, CI/CD, Git, Python</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Copilot, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d83c4d4db97873d5</t>
+          <t>https://www.indeed.com/viewjob?jk=e3f3d1cfcba7c70a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Kanini Software Solutions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Synapse, FastAPI, Docker, CI/CD, Git, PostgreSQL, Python, SQL</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1307a713db0f777e</t>
+          <t>https://www.indeed.com/viewjob?jk=302a1da90b16d922</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Python Develper</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, FAISS, Pinecone, TensorFlow, PyTorch, Docker, CI/CD, Python</t>
+          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e13a41dc86b5f36</t>
+          <t>https://www.indeed.com/viewjob?jk=bbf34bc79bfee29e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Salesforce AI / Einstein Developer</t>
+          <t>AI/ML - Applied AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Databricks, PySpark, Python</t>
+          <t>AI Engineer, CI/CD, Git, NoSQL, Tableau, Power BI, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1dc72753ea7cc45</t>
+          <t>https://www.indeed.com/viewjob?jk=d0106965447754c2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Engineer - Python | TheLoops</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IFS</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Hugging Face, Pinecone, Prompt Engineering, CI/CD, Git, Python, R</t>
+          <t>Data Scientist, RAG, S3, CI/CD, Git, Snowflake, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dbda87738776d31</t>
+          <t>https://www.indeed.com/viewjob?jk=65fa1c79d7085ebe</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, Python</t>
+          <t>LangChain, RAG, Kubernetes, CI/CD, Kafka, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=194261bb31192fd7</t>
+          <t>https://www.indeed.com/viewjob?jk=12105c95d6984da5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>IT Data Scientist - Level 2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Cintas</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, Python</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, Data Lake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d9a4c8885c90b5e</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ece90309525acf</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Salesforce AI / Einstein Developer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vikara.AI</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Databricks, PySpark, Python, SQL</t>
+          <t>AI Engineer, Git, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1de12f8e3dbaff6a</t>
+          <t>https://www.indeed.com/viewjob?jk=a2e55d2cbf984928</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Software Engineer II (AI)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ignite Insurance Systems</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Python, R</t>
+          <t>Generative AI, RAG, Prompt Engineering, Git, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77901b3684582750</t>
+          <t>https://www.indeed.com/viewjob?jk=c8119809830759b4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>GenAI Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Plante Moran</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Southfield, MI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, Databricks, PySpark, Power BI, Python, SQL</t>
+          <t>Data Scientist, RAG, Copilot, FastAPI, CI/CD, Databricks, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,392 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39cd370d20d11526</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Senior Specialist - Data Sciences</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>LTIMindtree</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, TensorFlow, PyTorch, FastAPI, Docker, Python</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=27e9c6f1ee3f0d44</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>CliftonLarsonAllen</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, CI/CD, Git, Databricks, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=70951b37d700924a</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>OpenAM</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, LLaMA, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, R, Scala</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c8634ea4c64bebbd</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>App Dev &amp; Database Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Metropolitan Transportation Authority</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, MongoDB, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d90360aa81ba0097</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>AI Developer</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Global Linking Solutions</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f332ae252b459a91</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Senior Integration Developer - Higher Education Exp Required</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Unitek Learning</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Tempe, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Git, Kafka, PostgreSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d8c7c0b2b396d994</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Servpro Industries</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Gallatin, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Git, Tableau, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d3821e24a55046e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Senior Consultant, Full Stack Engineer - Digital &amp; Insights</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>FTI Consulting, Inc.</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=539b056b17636737</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Software Engineer - FS/FE</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Rent the Runway</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Brooklyn, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Prompt Engineering, MySQL, MongoDB, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=31fdbe21f7b1ae69</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>CrowdStrike AI Security Engineer</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Generative AI, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8396490895a99087</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Mid-Senior Python/TensorFlow Developer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Devengine</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, Copilot, TensorFlow, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=385506505ec07794</t>
+          <t>https://www.indeed.com/viewjob?jk=480d60b7a60500ed</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-24.xlsx
+++ b/daily_matches/job_matches_2026-03-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Scientist I &amp; II</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FedEx</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26.7</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, BigQuery, Synapse, Dataflow</t>
+          <t>Data Scientist, RAG, Prompt Engineering, Data Lake, Docker, Kubernetes, CI/CD, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc7cdb95523374c3</t>
+          <t>https://www.indeed.com/viewjob?jk=0d2d9cf01e65cfd8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, MarTech</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Kiely Family of Companies</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tinton Falls, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>25.6</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, TensorFlow, PyTorch, AWS SageMaker</t>
+          <t>Copilot, Redshift, BigQuery, Git, Snowflake, Databricks, BigQuery, Redshift, PostgreSQL, Tableau</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1daebb30fd5fc85c</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b2ba9ffb9a799d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tror</t>
+          <t>The Clearing House Payments Company</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Liberty, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Copilot, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>RAG, Glue, Kinesis, CI/CD, Terraform, Git, Kafka, Tableau, Quicksight, Matplotlib</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3f3d1cfcba7c70a</t>
+          <t>https://www.indeed.com/viewjob?jk=beb95949bff9aca2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kanini Software Solutions</t>
+          <t>Waséyabek Development Company</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Otsego, MI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, FAISS, Pinecone, Prompt Engineering</t>
+          <t>RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=302a1da90b16d922</t>
+          <t>https://www.indeed.com/viewjob?jk=467fe0059b658cf7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Python Develper</t>
+          <t>Artificial Intelligence Engineer II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Viva Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Copilot, Prompt Engineering, Azure ML, Data Lake, Power BI, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbf34bc79bfee29e</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3ce451a9a0298e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI/ML - Applied AI Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, CI/CD, Git, NoSQL, Tableau, Power BI, Python, SQL, R, Java</t>
+          <t>RAG, Kinesis, MLflow, FastAPI, CI/CD, Git, Snowflake, Kafka, Power BI, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0106965447754c2</t>
+          <t>https://www.indeed.com/viewjob?jk=d37428d214fe7e4f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, CI/CD, Git, Snowflake, Tableau, Python, SQL, R</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Git, Snowflake, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fa1c79d7085ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=4699bc408a86b3c2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>GenAI Developer (L2)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Innovatis Technologies Inc</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Kubernetes, CI/CD, Kafka, NoSQL, SQL, R, Java, Scala</t>
+          <t>Generative AI, LangChain, RAG, FAISS, Pinecone, Prompt Engineering, CI/CD, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12105c95d6984da5</t>
+          <t>https://www.indeed.com/viewjob?jk=1fb95a370dab0378</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IT Data Scientist - Level 2</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cintas</t>
+          <t>Mercari</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, Data Lake, Python, SQL, R</t>
+          <t>RAG, BigQuery, Dataflow, AKS, CI/CD, BigQuery, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ece90309525acf</t>
+          <t>https://www.indeed.com/viewjob?jk=69b773db1c488113</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Healthcare Integration Consultant - EDI 834 &amp; Eligibility</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vikara.AI</t>
+          <t>Proactive Logic Consulting Inc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Git, MySQL, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, RAG, Copilot, CI/CD, Git, Databricks, Kafka, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,77 +811,952 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2e55d2cbf984928</t>
+          <t>https://www.indeed.com/viewjob?jk=91d870a9f33a600b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer II (AI)</t>
+          <t>Software Engineer - Full Stack (EAA - Compliance)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ignite Insurance Systems</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, Git, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Kubernetes, Terraform, Snowflake, Kafka, MongoDB, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8119809830759b4</t>
+          <t>https://www.indeed.com/viewjob?jk=4577a3ce998c3da0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GenAI Platform Engineer</t>
+          <t>Cyber Operations, Associate / Wilmington, DE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, Kubernetes, Apache Airflow, CI/CD, Terraform, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0c8f02922400f1e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Salesforce Administrator - Austin, TX ONLY</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>The New IEM, LLC</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Berwick, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Redshift, CI/CD, Git, Snowflake, Redshift, Tableau, Power BI, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93c4b0a2ec746891</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Data Platform</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Copilot, Data Lake, Kafka, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1db031a482b919c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>OST, Inc.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Data Scientist, Glue, Databricks, NoSQL, Tableau, Power BI, Quicksight, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2066334a8caadcc5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SDET</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Township of Hamilton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Copilot, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc49399df060bfe1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Production Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CyberArk</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e8f6ee57896bca19</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AI Enablement Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Perry Homes</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Copilot, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0da9be6497e0cf52</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Engineering Associate – API &amp; Automation Engineering</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Iselin, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1ae915705ea49db</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Consumer Engineering Test Infrastructure</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00319dfdd4ade3d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Quality Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Circle.so</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=235baa8877534de1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Cloud AI Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>10</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Copilot, FastAPI, CI/CD, Databricks, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=480d60b7a60500ed</t>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, PyTorch, Keras, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ca0b5ab2019e7b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Xactus</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Broomall, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>S3, Docker, CI/CD, GitHub Actions, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b67a92a7cbf1a596</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Java Full Stack Engineer (contract)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>BNY</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Kubernetes, AKS, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=52df93c65d7b5275</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Support Engineer (Java)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Smarsh</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=997399a7e5e52af4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Support Engineer (Java)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Smarsh</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7aab831c10ba87dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Support Engineer (Java)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Smarsh</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=60c4121549836952</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Support Engineer (Java)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Smarsh</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4434059b3943ebfc</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Support Engineer (Java)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Smarsh</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Pleasanton, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=065edca9716df967</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (AI Platform - AI Acceleration)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Gemini, Copilot, Prompt Engineering, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8fc26c6723684644</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (EAA)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Terraform, Kafka, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f931d799628d540</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Software Engineer, Data (Starlink)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SpaceX</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Hawthorne, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Kafka, PostgreSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3bde469e3f259001</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Operations Research</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>United Airlines</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, AKS, Git, Python, R, Java, Julia, Optimization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4061db3696df924e</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Retail Onchain (Borrow/Lend/Earn)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Gemini, Copilot, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f152de9728c9441</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Data Scientist II - Identity and Access</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Gemini, Copilot, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d2957bd80e938a13</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Customer Experience</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Gemini, Copilot, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8bebab45bc4abb69</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Institutional</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Gemini, Copilot, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d7ffd31cbe5403b</t>
         </is>
       </c>
     </row>
